--- a/CardGameRandom.xlsx
+++ b/CardGameRandom.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\Desktop\develop\c++\CardGame1\CardGame1(随机)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D138239-5E48-42A1-ABE4-19DB92634DC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E4E1B9C-6960-4452-9ABE-CCAE2CB42CF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="20057" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4217" yWindow="3051" windowWidth="24694" windowHeight="14598" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Role" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="10">
   <si>
     <t>CID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -79,6 +79,14 @@
       </rPr>
       <t>0%的概率攻击力x2</t>
     </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击数量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>防御数量</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -408,16 +416,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.15" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="10.69140625" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.69140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.69140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9" style="1"/>
+    <col min="3" max="6" width="15.69140625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="25.69140625" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -427,14 +435,20 @@
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -444,54 +458,60 @@
       <c r="C2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="1">
+        <v>3</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="1">
+        <v>4</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>10</v>
       </c>
